--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -657,7 +657,7 @@
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Pasted cell class 1 of 3 — audited and disclosed history</t>
+          <t>Pasted cell class 1 of 4 — audited and disclosed history</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Pasted cell class 2 of 3 — the unit build's output</t>
+          <t>Pasted cell class 2 of 4 — the unit build's output</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Pasted cell class 3 of 3 — whole-model re-runs</t>
+          <t>Pasted cell class 3 of 4 — whole-model re-runs</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -693,46 +693,58 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blue means input, black means formula</t>
+          <t>Pasted cell class 4 of 4 — the measured-error multipliers</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Blue type is a pasted number. Black type is calculated in the sheet.</t>
+          <t>The factors behind the far-year ranges at the foot of the Income Statement sheet. They are a measurement of how far this method's own projections have landed from what the company later reported, so they are an observation and not something the model can derive. The ranges they produce ARE formulas and move with the projection above them.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>The contested judgement is carried both ways</t>
+          <t>Blue means input, black means formula</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>The credit-loss and provision charge is the study's single most consequential contested judgement. Frame A treats it as a permanent cost of doing business; Frame B treats it as normalising. Both run all the way through to a value per share and both are published. They are never averaged into one number.</t>
+          <t>Blue type is a pasted number. Black type is calculated in the sheet.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Currency and units</t>
+          <t>The contested judgement is carried both ways</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Egyptian pounds. Money in millions unless a row says otherwise; per-share figures in pounds; packs and units in millions.</t>
+          <t>The credit-loss and provision charge is the study's single most consequential contested judgement. Frame A treats it as a permanent cost of doing business; Frame B treats it as normalising. Both run all the way through to a value per share and both are published. They are never averaged into one number.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Currency and units</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Egyptian pounds. Money in millions unless a row says otherwise; per-share figures in pounds; packs and units in millions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>Basis and date</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Audited CONSOLIDATED financial statements. Share price 127.30 at 2026-08-06; 168.755750 million shares in issue. Fiscal year ends 31 December.</t>
         </is>
@@ -2768,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>52.87174617751678</v>
+        <v>45.68528385393408</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>43.91794786985742</v>
+        <v>37.81150099018128</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>30.60944067360987</v>
+        <v>26.01416352323024</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>25.53445407113366</v>
+        <v>21.4844134990437</v>
       </c>
     </row>
     <row r="7">
@@ -2812,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>24.89238838802118</v>
+        <v>22.8494533223467</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>27.08100396297257</v>
+        <v>24.47046167069734</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>29.6689241928033</v>
+        <v>26.3649795393194</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>32.78882816716791</v>
+        <v>28.621995629933</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
     </row>
     <row r="10">
@@ -2840,7 +2852,7 @@
         <v>0.55</v>
       </c>
       <c r="D10" s="51" t="n">
-        <v>0.629</v>
+        <v>0.6658188407423365</v>
       </c>
       <c r="E10" s="51" t="n">
         <v>0.75</v>
@@ -2856,19 +2868,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>46.48276755483419</v>
+        <v>42.16724285094727</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>40.68048040441269</v>
+        <v>36.76279124931227</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>31.21093776529835</v>
+        <v>27.93707835693304</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>25.51161940550458</v>
+        <v>22.62112480563719</v>
       </c>
     </row>
     <row r="13">
@@ -2900,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>55.90961031827637</v>
+        <v>49.26491319840814</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>48.90229665122401</v>
+        <v>42.7590534998364</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>27.88035565006691</v>
+        <v>23.24147440412117</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>17.3693851494884</v>
+        <v>13.4826848562636</v>
       </c>
     </row>
     <row r="16">
@@ -2944,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>50.75521953556864</v>
+        <v>44.63956596764732</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>43.69735863472546</v>
+        <v>38.00668249749155</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>29.5816368330391</v>
+        <v>24.74091555718003</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>22.52377593219603</v>
+        <v>18.10803208702435</v>
       </c>
     </row>
     <row r="19">
@@ -2988,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>42.79873970509544</v>
+        <v>37.36532565503385</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>39.82120218385909</v>
+        <v>34.4684633681824</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>33.24239702293765</v>
+        <v>28.0704744073638</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>29.61825605669214</v>
+        <v>24.54723077671931</v>
       </c>
     </row>
     <row r="22">
@@ -3032,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>42.54294576364056</v>
+        <v>36.77869012904124</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>38.99364180915672</v>
+        <v>33.53006026952217</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>34.07581530837081</v>
+        <v>29.02402305899556</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>31.05447660436835</v>
+        <v>26.252358655231</v>
       </c>
     </row>
     <row r="25">
@@ -3076,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>33.91980523946785</v>
+        <v>31.34494284548571</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>37.23017363970158</v>
+        <v>33.89811072289919</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>41.26937562789497</v>
+        <v>36.98163985573206</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>46.32742747255725</v>
+        <v>40.80133138880694</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>52.87174617751678</v>
+        <v>45.68528385393408</v>
       </c>
     </row>
     <row r="27">
@@ -3098,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>29.09798312781783</v>
+        <v>26.81224996276908</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>31.778273158147</v>
+        <v>28.8405802906386</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>34.99453268848002</v>
+        <v>31.24838047980015</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>38.94086106863173</v>
+        <v>34.1699621733944</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>43.91794786985742</v>
+        <v>37.81150099018128</v>
       </c>
     </row>
     <row r="28">
@@ -3120,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>24.89238838802118</v>
+        <v>22.8494533223467</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>27.08100396297257</v>
+        <v>24.47046167069734</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>29.6689241928033</v>
+        <v>26.3649795393194</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>32.78882816716791</v>
+        <v>28.621995629933</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>31.37379902733586</v>
       </c>
     </row>
     <row r="29">
@@ -3142,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>21.19463710773727</v>
+        <v>19.35781412337375</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>22.99461214749164</v>
+        <v>20.65893665542676</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>25.09520754686392</v>
+        <v>22.15790078568526</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>27.5887007173728</v>
+        <v>23.9142656428088</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>30.60944067360987</v>
+        <v>26.01416352323024</v>
       </c>
     </row>
     <row r="30">
@@ -3164,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>17.92025263747544</v>
+        <v>16.26006785654848</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>19.40957317966708</v>
+        <v>17.3073954172165</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>21.12709566972723</v>
+        <v>18.49776590833174</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>23.13790859590948</v>
+        <v>19.87124732344099</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>25.53445407113366</v>
+        <v>21.4844134990437</v>
       </c>
     </row>
     <row r="32">
@@ -3193,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>7982.760359839642</v>
+        <v>9321.885127781243</v>
       </c>
     </row>
     <row r="34">
@@ -3203,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.3002077087568915</v>
+        <v>0.3337598757730512</v>
       </c>
     </row>
     <row r="35">
@@ -3213,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>113.854176701619</v>
+        <v>132.9534532778984</v>
       </c>
     </row>
     <row r="36">
@@ -3223,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.138541767016189</v>
+        <v>1.329534532778984</v>
       </c>
     </row>
   </sheetData>
@@ -3903,7 +3915,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 81% of core enterprise value, 63% of total</t>
+          <t>Terminal value 79% of core enterprise value, 61% of total</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3935,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 81% of core enterprise value, 66% of total</t>
+          <t>Terminal value 79% of core enterprise value, 64% of total</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3955,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.19 times book</t>
+          <t>Justified 1.16 times book</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5430,7 @@
         </is>
       </c>
       <c r="C49" s="22" t="n">
-        <v>0.629</v>
+        <v>0.6658188407423365</v>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
@@ -8771,11 +8783,11 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal NOPAT = final-year NOPAT x (1 + growth), less the depreciation the parked construction balance has never been charged</t>
+          <t>Terminal NOPAT, on FY2030E money = final-year NOPAT less the depreciation the parked construction balance has never been charged. It is NOT grown here: the terminal value row below grows the whole free cash flow one year</t>
         </is>
       </c>
       <c r="B21" s="13">
-        <f>F8*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10)</f>
+        <f>F8-B20*(1-Assumptions!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -8786,7 +8798,7 @@
         </is>
       </c>
       <c r="B22" s="13">
-        <f>452.701729</f>
+        <f>423.085728</f>
         <v/>
       </c>
     </row>
@@ -8797,7 +8809,7 @@
         </is>
       </c>
       <c r="B23" s="13">
-        <f>-722.038275</f>
+        <f>-674.802126</f>
         <v/>
       </c>
     </row>
@@ -8819,7 +8831,7 @@
         </is>
       </c>
       <c r="B25" s="13">
-        <f>-767.671686</f>
+        <f>-717.450174</f>
         <v/>
       </c>
     </row>
@@ -9051,11 +9063,11 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Terminal NOPAT on Frame B, less the parked construction depreciation</t>
+          <t>Terminal NOPAT on Frame B, on FY2030E money, less the parked construction depreciation — not grown here, for the same reason as Frame A</t>
         </is>
       </c>
       <c r="B43" s="13">
-        <f>F39*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10)</f>
+        <f>F39-B20*(1-Assumptions!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -9066,7 +9078,7 @@
         </is>
       </c>
       <c r="B44" s="13">
-        <f>B43+-1037.008231</f>
+        <f>B43+-969.166571</f>
         <v/>
       </c>
     </row>
@@ -9114,7 +9126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10115,6 +10127,307 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>YEARS THREE TO FIVE AS RANGES — the method replayed on this company's own past, year by year, and scored against what was later reported</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Readings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>MULTIPLY the projection by the factor: above one means the outturn came in ABOVE the projection. The basis is a SPAN — the widest and the narrowest of the readings behind it, never a percentile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Revenue — low of the range</t>
+        </is>
+      </c>
+      <c r="G31" s="13">
+        <f>G2*K31</f>
+        <v/>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="n">
+        <v>1.731530386298975</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Revenue — high of the range</t>
+        </is>
+      </c>
+      <c r="G32" s="13">
+        <f>G2*K32</f>
+        <v/>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>2.023455302609483</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Cost of sales — low of the range</t>
+        </is>
+      </c>
+      <c r="G33" s="13">
+        <f>G3*K33</f>
+        <v/>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="n">
+        <v>1.646500820627678</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Cost of sales — high of the range</t>
+        </is>
+      </c>
+      <c r="G34" s="13">
+        <f>G3*K34</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="n">
+        <v>1.946898481956563</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Gross profit — low of the range</t>
+        </is>
+      </c>
+      <c r="G35" s="13">
+        <f>G6*K35</f>
+        <v/>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="n">
+        <v>1.830389697781688</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Gross profit — high of the range</t>
+        </is>
+      </c>
+      <c r="G36" s="13">
+        <f>G6*K36</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="n">
+        <v>2.130056265290247</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Profit for the year — low of the range</t>
+        </is>
+      </c>
+      <c r="G37" s="13">
+        <f>G24*K37</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="n">
+        <v>1.719212803624718</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Profit for the year — high of the range</t>
+        </is>
+      </c>
+      <c r="G38" s="13">
+        <f>G24*K38</f>
+        <v/>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="n">
+        <v>3.405013586428177</v>
+      </c>
+      <c r="L38" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation — low of the range</t>
+        </is>
+      </c>
+      <c r="G39" s="13">
+        <f>G16*K39</f>
+        <v/>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="n">
+        <v>0.56170003273404</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation — high of the range</t>
+        </is>
+      </c>
+      <c r="G40" s="13">
+        <f>G16*K40</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="n">
+        <v>0.6032344004250967</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The fourth and fifth forecast years carry no measured range: the replay covers three years ahead and no further, and none is invented for them.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
